--- a/examples/excel/charts/charts-scatter.xlsx
+++ b/examples/excel/charts/charts-scatter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Scatter Fundamentals" sheetId="2" r:id="R27dee062f8f34b61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Marker Styles" sheetId="3" r:id="R24ecd47d51884d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Trendlines" sheetId="4" r:id="R0a8cc75c808a46f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Error Bars" sheetId="5" r:id="R0aa85440183f486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Styling" sheetId="6" r:id="R7080f118500049a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-Advanced" sheetId="7" r:id="Rb27a2e9e329c4469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Scatter Fundamentals" sheetId="2" r:id="R9014addbe0f3472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Marker Styles" sheetId="3" r:id="R3f7d4d7db96644d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Trendlines" sheetId="4" r:id="R1f5f3f80fc0f47c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Error Bars" sheetId="5" r:id="R9cb660d19b704191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Styling" sheetId="6" r:id="R783eb78a474c420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-Advanced" sheetId="7" r:id="Rf0319e5089744801"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45,7 +45,11 @@
             <c:v>Male</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -111,7 +115,11 @@
             <c:v>Female</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -266,8 +274,16 @@
           <c:tx>
             <c:v>Measurement</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:marker>
             <c:symbol val="square"/>
+            <c:size val="7"/>
           </c:marker>
           <c:trendline>
             <c:trendlineType val="poly"/>
@@ -343,11 +359,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -445,8 +456,16 @@
           <c:tx>
             <c:v>Growth</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:marker>
             <c:symbol val="triangle"/>
+            <c:size val="7"/>
           </c:marker>
           <c:trendline>
             <c:trendlineType val="exp"/>
@@ -511,11 +530,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -613,66 +627,71 @@
           <c:tx>
             <c:v>Dataset A</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="7"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>16</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>32</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>64</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="7"/>
-              <c:pt idx="0">
-                <c:v>10</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>18</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>30</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>62</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>78</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>95</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:size val="7"/>
           </c:marker>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>16</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>64</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>10</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>18</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>62</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>78</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>95</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -680,66 +699,71 @@
           <c:tx>
             <c:v>Dataset B</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="7"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>16</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>32</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>64</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="7"/>
-              <c:pt idx="0">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>38</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>54</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>56</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:size val="7"/>
           </c:marker>
+          <c:trendline>
+            <c:trendlineType val="log"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>16</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>64</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>54</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>56</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -820,7 +844,11 @@
             <c:v>Measurement</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -993,7 +1021,11 @@
             <c:v>Yield</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -1166,7 +1198,11 @@
             <c:v>Trial 1</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="square"/>
@@ -1243,7 +1279,11 @@
             <c:v>Trial 2</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="9DC3E6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="square"/>
@@ -1392,7 +1432,11 @@
             <c:v>Experiment</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="843C0B"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -1996,7 +2040,11 @@
             <c:v>Readings</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -2208,72 +2256,74 @@
           <c:tx>
             <c:v>Class A</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>8</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>55</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>60</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>65</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>72</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>78</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>82</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>88</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>92</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:size val="8"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>8</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>65</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>72</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>78</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>82</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>88</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>92</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2281,72 +2331,74 @@
           <c:tx>
             <c:v>Class B</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>8</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>62</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>68</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>74</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>80</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>85</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>90</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:size val="8"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>8</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>62</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>68</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>74</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>85</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>90</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -2455,7 +2507,11 @@
             <c:v>Data</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="square"/>
@@ -2596,7 +2652,11 @@
             <c:v>Temperature (C)</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -2652,8 +2712,8 @@
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:scatterChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
@@ -2662,7 +2722,11 @@
             <c:v>Humidity (%)</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -2717,7 +2781,7 @@
         </c:ser>
         <c:axId val="3"/>
         <c:axId val="4"/>
-      </c:lineChart>
+      </c:scatterChart>
       <c:valAx>
         <c:axId val="1"/>
         <c:scaling>
@@ -2757,24 +2821,6 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1400" b="1"/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1400" b="1"/>
-                  <a:t>Location</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
@@ -2793,7 +2839,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -2840,7 +2886,11 @@
             <c:v>Score</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -3042,7 +3092,11 @@
             <c:v>Response</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="triangle"/>
@@ -3188,67 +3242,11 @@
           <c:tx>
             <c:v>KPI</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>8</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>62</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>38</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>78</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>55</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>82</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>48</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>90</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
@@ -3318,6 +3316,64 @@
               </a:solidFill>
             </c:spPr>
           </c:dPt>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>8</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>62</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>78</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>82</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>90</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
@@ -3424,7 +3480,11 @@
             <c:v>Sales ($)</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -3588,64 +3648,67 @@
           </c:tx>
           <c:spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="7"/>
-              <c:pt idx="0">
-                <c:v>0</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>500</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>1000</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>2000</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>3000</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>5000</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>8000</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="7"/>
-              <c:pt idx="0">
-                <c:v>1013</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>955</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>899</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>795</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>701</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>540</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>356</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>500</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1000</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>2000</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>3000</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>5000</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>8000</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>1013</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>955</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>899</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>795</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>701</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>540</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>356</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -3744,8 +3807,16 @@
             <c:v>Sensor A</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="6"/>
@@ -3792,9 +3863,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="8"/>
-          </c:marker>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -3803,8 +3871,16 @@
             <c:v>Sensor B</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="6"/>
@@ -3851,9 +3927,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="8"/>
-          </c:marker>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -3862,8 +3935,16 @@
             <c:v>Sensor C</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="6"/>
@@ -3910,9 +3991,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="8"/>
-          </c:marker>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -3993,8 +4071,16 @@
             <c:v>Lab 1</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="9"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="6"/>
@@ -4041,9 +4127,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="9"/>
-          </c:marker>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -4052,8 +4135,16 @@
             <c:v>Lab 2</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="9DC3E6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="star"/>
+            <c:size val="9"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="6"/>
@@ -4100,9 +4191,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="9"/>
-          </c:marker>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -4111,8 +4199,16 @@
             <c:v>Lab 3</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="843C0B"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="x"/>
+            <c:size val="9"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="6"/>
@@ -4159,9 +4255,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="9"/>
-          </c:marker>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -4241,54 +4334,57 @@
           <c:tx>
             <c:v>Revenue</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>100</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>200</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>300</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>400</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>500</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>150</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>280</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>350</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>420</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>510</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
+            <c:symbol val="circle"/>
             <c:size val="10"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>200</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>300</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>400</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>500</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>150</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>280</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>350</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>420</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>510</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -4296,54 +4392,57 @@
           <c:tx>
             <c:v>Profit</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>100</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>200</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>300</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>400</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>500</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>80</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>140</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>180</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>220</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>280</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
+            <c:symbol val="plus"/>
             <c:size val="10"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>200</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>300</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>400</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>500</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>140</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>180</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>220</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>280</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -4351,54 +4450,57 @@
           <c:tx>
             <c:v>Cost</c:v>
           </c:tx>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>100</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>200</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>300</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>400</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>500</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>70</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>140</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>170</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>200</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>230</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="BF8F00"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
+            <c:symbol val="dash"/>
             <c:size val="10"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>200</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>300</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>400</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>500</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>70</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>140</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>170</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>200</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>230</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -4480,82 +4582,85 @@
           </c:tx>
           <c:spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
               <a:prstDash val="sysDashDot"/>
             </a:ln>
           </c:spPr>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>11</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>12</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>18</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>15</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>20</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="10"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>10</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="10"/>
+              <c:pt idx="0">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>14</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>18</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>15</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>20</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -4565,82 +4670,85 @@
           </c:tx>
           <c:spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="BFBFBF"/>
+              </a:solidFill>
               <a:prstDash val="sysDashDot"/>
             </a:ln>
           </c:spPr>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>10</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>12</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>11</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="10"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>10</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="10"/>
+              <c:pt idx="0">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>10</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>11</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -4720,87 +4828,89 @@
           <c:tx>
             <c:v>Observed</c:v>
           </c:tx>
-          <c:trendline>
-            <c:trendlineType val="linear"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numLit>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>15</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>28</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>33</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>48</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>55</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>60</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>68</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:size val="7"/>
           </c:marker>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="10"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>10</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="10"/>
+              <c:pt idx="0">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>15</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>33</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>68</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -4892,7 +5002,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb707eabdc0d1441a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R548a880c4a1547d0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4922,7 +5032,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R664609d8bc4845ca"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae2b7444125f46b0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4952,7 +5062,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bd4b57558824c92"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R30021b52c76c4eae"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4982,7 +5092,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5998b81a1bc74f05"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4945cdf9f52b4bc4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5017,7 +5127,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9cbbd9c79d964054"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23620bc0faa940c9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5047,7 +5157,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1e8c3e9bdef94fcf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R000f5263f51b443c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5077,7 +5187,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc20fee8b05804f56"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3a3862d08558425a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5107,7 +5217,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R09ca1fbc4acf4d9a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6169c4af80be4033"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5142,7 +5252,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R70150fca461e4906"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R463bd3fb58e648ae"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5172,7 +5282,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2beaa5e6dccd48cf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2be41817692b4f6c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5202,7 +5312,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3075966740d44184"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R41a6ce56839e4e83"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5232,7 +5342,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1eb63e0e40fd49f7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd20f0b76441546c5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5267,7 +5377,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0653747722524d27"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f772bb9bf564998"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5297,7 +5407,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R88d516996ea640df"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re3f95624930942ef"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5327,7 +5437,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R57abb1b5fbfc47ef"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc0aead66fbb64c34"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5357,7 +5467,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e62f10504444388"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdccfb19e33b54be2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5392,7 +5502,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f346d5d902f4b38"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re3cea232b5ca491f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5422,7 +5532,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a8ce9726b0c4b8f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R52d04bf2e63c420e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5452,7 +5562,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c70d3073c124309"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R84d3749d355a4b4d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5482,7 +5592,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re079b186213448db"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R62db6addd7d246e6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5517,7 +5627,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1c5746f70a74167"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8ac740e53ea44fb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5547,7 +5657,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R42eedd29f9264676"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re15103e1e1f44cb7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5577,7 +5687,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4b8b72fbc8774233"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fbe39a3b55848a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5607,7 +5717,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra34cee4b7aa64d1e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00116b0d2c9d45cf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5616,44 +5726,153 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdde61e2afd84483"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b75d84ce6764d1c"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b04ba15110e4939"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radb58146d6e94cc8"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cc4d38a97984de1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4f6171364d94bec"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra80c2e9e05d543fd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2050bbbcd4f9432f"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ff1a82ceb804267"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16f52cab4d464d31"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ed7d6a8bfc94c32"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra257e1e176ff4de8"/>
 </x:worksheet>
 </file>